--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753759</v>
       </c>
       <c r="B2" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753759</v>
       </c>
       <c r="B2" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127753636</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127753681</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>127753880</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753759</v>
       </c>
       <c r="B2" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127753636</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127753681</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>127753880</v>
       </c>
       <c r="B5" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753759</v>
       </c>
       <c r="B2" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753759</v>
       </c>
       <c r="B2" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753759</v>
       </c>
       <c r="B2" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,6 +1083,795 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128468968</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97353</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Båstorp, Båstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>331704</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6431005</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flertalet plantor ca  2 kvm yta</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128468341</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97353</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Båstorp, Båstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>331731</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6431019</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flertalet plantor ca 2 kvm</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128468993</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97353</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Båstorp, Båstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>331704</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6431010</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128469709</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58532</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Båstorp, Båstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>331662</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6431050</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128474955</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91779</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Båstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>331668</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6431035</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer ihop med tallrot</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128469041</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97353</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Båstorp, Båstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>331675</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6431033</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128469596</v>
+      </c>
+      <c r="B12" t="n">
+        <v>95718</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Båstorp, Båstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>331655</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6431060</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753759</v>
       </c>
       <c r="B2" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127753636</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127753681</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>127753880</v>
       </c>
       <c r="B5" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97353</v>
+        <v>97355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97353</v>
+        <v>97355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97353</v>
+        <v>97355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128469709</v>
+        <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>58532</v>
+        <v>91779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1467,24 +1467,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Båstorp, Båstorp, Vg</t>
+          <t>Båstorp, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>331662</v>
+        <v>331668</v>
       </c>
       <c r="R9" t="n">
-        <v>6431050</v>
+        <v>6431035</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,19 +1509,14 @@
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:20</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer ihop med tallrot</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,6 +1525,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1550,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128474955</v>
+        <v>128469709</v>
       </c>
       <c r="B10" t="n">
-        <v>91779</v>
+        <v>58532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1583,22 +1577,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Båstorp, Vg</t>
+          <t>Båstorp, Båstorp, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>331668</v>
+        <v>331662</v>
       </c>
       <c r="R10" t="n">
-        <v>6431035</v>
+        <v>6431050</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1625,14 +1621,19 @@
           <t>2025-09-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer ihop med tallrot</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1642,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97353</v>
+        <v>97355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95718</v>
+        <v>95720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127753759</v>
       </c>
       <c r="B2" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127753636</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127753681</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>127753880</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95720</v>
+        <v>95813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,6 +1871,222 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128486018</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102800</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Båstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>331753</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6431023</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128493965</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92084</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Båstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>331695</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6431032</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>91779</v>
+        <v>91871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>128469709</v>
       </c>
       <c r="B10" t="n">
-        <v>58532</v>
+        <v>58544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>91871</v>
+        <v>91877</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>128469709</v>
       </c>
       <c r="B10" t="n">
-        <v>58544</v>
+        <v>58548</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95813</v>
+        <v>95819</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102800</v>
+        <v>102811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92084</v>
+        <v>92090</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>91877</v>
+        <v>91883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95819</v>
+        <v>95825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102811</v>
+        <v>102819</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>91883</v>
+        <v>91885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95825</v>
+        <v>95827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102819</v>
+        <v>102829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102829</v>
+        <v>102835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95827</v>
+        <v>95828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102835</v>
+        <v>102836</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102836</v>
+        <v>102863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>91886</v>
+        <v>91913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>128469709</v>
       </c>
       <c r="B10" t="n">
-        <v>58548</v>
+        <v>58575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95828</v>
+        <v>95855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102863</v>
+        <v>102869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>91913</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95855</v>
+        <v>95868</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102869</v>
+        <v>102876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102876</v>
+        <v>102880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>91923</v>
+        <v>91927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>128469709</v>
       </c>
       <c r="B10" t="n">
-        <v>58575</v>
+        <v>58579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1088,7 +1088,7 @@
         <v>128468968</v>
       </c>
       <c r="B6" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128468341</v>
       </c>
       <c r="B7" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128468993</v>
       </c>
       <c r="B8" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128474955</v>
       </c>
       <c r="B9" t="n">
-        <v>91927</v>
+        <v>91932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>128469709</v>
       </c>
       <c r="B10" t="n">
-        <v>58579</v>
+        <v>58582</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128469041</v>
       </c>
       <c r="B11" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>128469596</v>
       </c>
       <c r="B12" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128486018</v>
       </c>
       <c r="B13" t="n">
-        <v>102880</v>
+        <v>102887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37005-2025 artfynd.xlsx
+++ b/artfynd/A 37005-2025 artfynd.xlsx
@@ -1992,7 +1992,7 @@
         <v>128493965</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
